--- a/data/guerra_mafias_3.xlsx
+++ b/data/guerra_mafias_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CCE4AF-1CBD-417E-B632-5B3F2F53EF55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3998FB2-7332-4974-BC11-7DACEF006EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batallas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1356" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="207">
   <si>
     <t>player1</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Fase de grupos</t>
   </si>
   <si>
-    <t>[Gen 9] National Dex Doubles</t>
-  </si>
-  <si>
     <t>Replay</t>
   </si>
   <si>
@@ -167,15 +164,9 @@
     <t>2026-10-17</t>
   </si>
   <si>
-    <t>[Gen 9] Random Doubles Battle</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9randomdoublesbattle-2700031976</t>
   </si>
   <si>
-    <t>[Gen 9] Random Battle</t>
-  </si>
-  <si>
     <t>SINGLES</t>
   </si>
   <si>
@@ -185,9 +176,6 @@
     <t>2026-10-06</t>
   </si>
   <si>
-    <t>[Gen 9] OU</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9ou-2693959332</t>
   </si>
   <si>
@@ -197,15 +185,9 @@
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2695699817</t>
   </si>
   <si>
-    <t>[Gen 9] Doubles Ubers</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9doublesubers-2697931632</t>
   </si>
   <si>
-    <t>[Gen 9 Champions] VGC 2026 Reg M-B (Bo3)</t>
-  </si>
-  <si>
     <t>VGC</t>
   </si>
   <si>
@@ -224,36 +206,21 @@
     <t>2026-10-18</t>
   </si>
   <si>
-    <t>[Gen 9 Champions] OU</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9championsou-2700657221-xexnwtfcr5tarh9yi3lj4pwmf9j5a1fpw</t>
   </si>
   <si>
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2700016465</t>
   </si>
   <si>
-    <t>David</t>
-  </si>
-  <si>
     <t>Clauz</t>
   </si>
   <si>
-    <t>[Gen 9] BSS Factory</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9bssfactory-2701296987</t>
   </si>
   <si>
     <t>Equipo 2</t>
   </si>
   <si>
-    <t>Lee</t>
-  </si>
-  <si>
-    <t>[Gen 9] Battle Factory</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9battlefactory-2695876014</t>
   </si>
   <si>
@@ -263,9 +230,6 @@
     <t>https://replay.pokemonshowdown.com/gen9battlefactory-2695860512</t>
   </si>
   <si>
-    <t>[Gen 9] National Dex</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9nationaldex-2701293423</t>
   </si>
   <si>
@@ -275,33 +239,21 @@
     <t>https://replay.pokemonshowdown.com/gen9doublesubers-2695871695</t>
   </si>
   <si>
-    <t>[Gen 6] VGC 2014</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen6vgc2014-2701291499</t>
   </si>
   <si>
     <t>2026-10-10</t>
   </si>
   <si>
-    <t>[Gen 9] National Dex Doubles Ubers</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9nationaldexdoublesubers-2696352414</t>
   </si>
   <si>
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2695857517</t>
   </si>
   <si>
-    <t>[Gen 9] Monotype Random Battle</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9monotyperandombattle-2696349068</t>
   </si>
   <si>
-    <t>Kroko</t>
-  </si>
-  <si>
     <t>Chescor</t>
   </si>
   <si>
@@ -314,9 +266,6 @@
     <t>Equipo 3</t>
   </si>
   <si>
-    <t>[Gen 7] OU</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen7ou-2696759981</t>
   </si>
   <si>
@@ -326,9 +275,6 @@
     <t>https://replay.pokemonshowdown.com/gen9nationaldex-2700607219-cx29hdj2mpv5rr9ksnaer1apjwvcahcpw</t>
   </si>
   <si>
-    <t>Chris</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen7ou-2696595548-xt1w3k5rqy691hyhsgr0ujl57lxxq17pw</t>
   </si>
   <si>
@@ -347,15 +293,9 @@
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2701946499-8gpac1h4y6qgbcxyyx1t1dampiii9a6pw</t>
   </si>
   <si>
-    <t>Adri</t>
-  </si>
-  <si>
     <t>Josar</t>
   </si>
   <si>
-    <t>[Gen 8] VGC 2021</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen8vgc2021-2701703506</t>
   </si>
   <si>
@@ -374,15 +314,9 @@
     <t>Arnaenaed ∾</t>
   </si>
   <si>
-    <t>Nube</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen8vgc2021-2700127756</t>
   </si>
   <si>
-    <t>[Gen 9] National Dex Monotype</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9nationaldexmonotype-2697860912</t>
   </si>
   <si>
@@ -398,12 +332,6 @@
     <t>https://replay.pokemonshowdown.com/gen9nationaldex-2700274464</t>
   </si>
   <si>
-    <t>Necrozzz</t>
-  </si>
-  <si>
-    <t>Draco</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9monotyperandombattle-2701958883</t>
   </si>
   <si>
@@ -434,21 +362,9 @@
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2700060447</t>
   </si>
   <si>
-    <t>[Gen 9] Doubles OU</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9doublesou-2701848615</t>
   </si>
   <si>
-    <t>Pou</t>
-  </si>
-  <si>
-    <t>Elin</t>
-  </si>
-  <si>
-    <t>[Gen 9] Monotype</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9monotype-2701646912-8jq9572b0oe3tc5ja017w1iyvd9gbdkpw</t>
   </si>
   <si>
@@ -464,15 +380,9 @@
     <t>https://replay.pokemonshowdown.com/gen9nationaldex-2693479499</t>
   </si>
   <si>
-    <t>Polar</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9ou-2696205271-8u037rwvm0scgaam3b99dqu6dayg9cypw</t>
   </si>
   <si>
-    <t>[Gen 9] Trademarked</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9trademarked-2696168430-s2ffqu9q5oajnmm7wvxjcj3ryyrmr03pw</t>
   </si>
   <si>
@@ -482,9 +392,6 @@
     <t>https://replay.pokemonshowdown.com/gen9nationaldexmonotype-2698519528-fnlcxcn2430sq3el0xnllfri31qw3tppw</t>
   </si>
   <si>
-    <t>[Gen 9 Champions] VGC 2026 Reg M-C</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9championsvgc2026regmc-2693481774</t>
   </si>
   <si>
@@ -515,18 +422,12 @@
     <t>Zanty</t>
   </si>
   <si>
-    <t>[Gen 2] Random Battle</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen2randombattle-2694047369-e6xpvwmpjyysvoyolw97365gsi4w75apw</t>
   </si>
   <si>
     <t>Wlaimer</t>
   </si>
   <si>
-    <t>[Gen 9] Random Battle Mayhem</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9randombattlemayhem-2701829151-m0t47kj40493tsrlqy2kw4aex6fvq40pw</t>
   </si>
   <si>
@@ -548,9 +449,6 @@
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2699343837-spy5w0r2u3wjpm7qldob862r7nedf7upw</t>
   </si>
   <si>
-    <t>[Gen 9 Champions] Random Battle</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9championsrandombattle-2701825331</t>
   </si>
   <si>
@@ -584,30 +482,18 @@
     <t>qdqwdqwdqwdqwd</t>
   </si>
   <si>
-    <t>[Gen 9] Battlefields</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9battlefields-2696654920</t>
   </si>
   <si>
-    <t>[Gen 9] Random Battle (Shared Power, B12P6)</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9randombattlesharedpowerb12p6-2693534320-9ntohu3rbjf3hhhf4bvi3gc8w9lgxwypw</t>
   </si>
   <si>
-    <t>[Gen 9] Partners in Crime</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9partnersincrime-2701964871</t>
   </si>
   <si>
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2700687517-bg4q0wjf9w4m0nqf2740l8jhewu70bopw</t>
   </si>
   <si>
-    <t>[Gen 8] National Dex</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen8nationaldex-2698001279-tjkg09teajsq0v2k65wmwmlkimd7sodpw</t>
   </si>
   <si>
@@ -708,6 +594,69 @@
   </si>
   <si>
     <t>Drixxard</t>
+  </si>
+  <si>
+    <t>NAT DEX DOBLES</t>
+  </si>
+  <si>
+    <t>RANDOM SINGLES</t>
+  </si>
+  <si>
+    <t>OU</t>
+  </si>
+  <si>
+    <t>VGC 2021</t>
+  </si>
+  <si>
+    <t>VGC 2014</t>
+  </si>
+  <si>
+    <t>NAT DEX</t>
+  </si>
+  <si>
+    <t>Battle Factory</t>
+  </si>
+  <si>
+    <t>NAT DEX DUBERS</t>
+  </si>
+  <si>
+    <t>NAT DEX MONOTYPE</t>
+  </si>
+  <si>
+    <t>RANDOM SINGLES B12P6</t>
+  </si>
+  <si>
+    <t>MONOTYPE RANDOM SINGLES</t>
+  </si>
+  <si>
+    <t>RANDOM SINGLES MAYHEM</t>
+  </si>
+  <si>
+    <t>BSS Factory</t>
+  </si>
+  <si>
+    <t>Battlefields</t>
+  </si>
+  <si>
+    <t>DOU</t>
+  </si>
+  <si>
+    <t>DUBERS</t>
+  </si>
+  <si>
+    <t>RANDOM DOUBLES</t>
+  </si>
+  <si>
+    <t>MONOTYPE</t>
+  </si>
+  <si>
+    <t>TRADERMARKED</t>
+  </si>
+  <si>
+    <t>Partners in Crime</t>
+  </si>
+  <si>
+    <t>Okar958</t>
   </si>
 </sst>
 </file>
@@ -1069,10 +1018,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="16" customWidth="1"/>
-    <col min="8" max="8" width="26" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="8" max="9" width="36" customWidth="1"/>
     <col min="10" max="10" width="42.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.140625" customWidth="1"/>
     <col min="13" max="14" width="26" customWidth="1"/>
     <col min="19" max="19" width="72.140625" customWidth="1"/>
     <col min="20" max="20" width="15.5703125" bestFit="1" customWidth="1"/>
@@ -1184,40 +1133,40 @@
         <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>186</v>
+      </c>
+      <c r="L2" t="s">
         <v>33</v>
       </c>
-      <c r="J2" t="s">
-        <v>32</v>
-      </c>
-      <c r="L2" t="s">
-        <v>34</v>
-      </c>
       <c r="M2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2" t="s">
         <v>35</v>
       </c>
-      <c r="N2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="T2">
+        <v>9</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA2" t="s">
         <v>36</v>
-      </c>
-      <c r="T2">
-        <v>9</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
@@ -1225,50 +1174,50 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
       </c>
       <c r="E3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>186</v>
+      </c>
+      <c r="L3" t="s">
+        <v>33</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3" t="s">
         <v>39</v>
       </c>
-      <c r="F3" t="s">
-        <v>30</v>
-      </c>
-      <c r="G3" t="s">
-        <v>31</v>
-      </c>
-      <c r="H3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>34</v>
-      </c>
-      <c r="M3" t="s">
-        <v>35</v>
-      </c>
-      <c r="N3" t="s">
-        <v>31</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>0</v>
-      </c>
-      <c r="S3" t="s">
-        <v>40</v>
-      </c>
       <c r="T3">
         <v>9</v>
       </c>
@@ -1276,7 +1225,7 @@
         <v>28</v>
       </c>
       <c r="AA3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -1284,50 +1233,50 @@
         <v>26</v>
       </c>
       <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
         <v>41</v>
       </c>
-      <c r="C4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>202</v>
+      </c>
+      <c r="L4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4" t="s">
         <v>42</v>
       </c>
-      <c r="F4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" t="s">
-        <v>43</v>
-      </c>
-      <c r="I4" t="s">
-        <v>33</v>
-      </c>
-      <c r="J4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>0</v>
-      </c>
-      <c r="S4" t="s">
-        <v>44</v>
-      </c>
       <c r="T4">
         <v>9</v>
       </c>
@@ -1335,7 +1284,7 @@
         <v>28</v>
       </c>
       <c r="AA4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -1361,19 +1310,19 @@
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N5" t="s">
         <v>31</v>
@@ -1385,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1394,7 +1343,7 @@
         <v>28</v>
       </c>
       <c r="AA5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.25">
@@ -1402,7 +1351,7 @@
         <v>27</v>
       </c>
       <c r="B6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
@@ -1411,7 +1360,7 @@
         <v>28</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
         <v>30</v>
@@ -1420,32 +1369,32 @@
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="L6" t="s">
+        <v>43</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" t="s">
+        <v>31</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6" t="s">
         <v>46</v>
       </c>
-      <c r="M6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N6" t="s">
-        <v>31</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6" t="s">
-        <v>50</v>
-      </c>
       <c r="T6">
         <v>9</v>
       </c>
@@ -1453,7 +1402,7 @@
         <v>28</v>
       </c>
       <c r="AA6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
@@ -1461,7 +1410,7 @@
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
         <v>27</v>
@@ -1470,7 +1419,7 @@
         <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F7" t="s">
         <v>30</v>
@@ -1479,19 +1428,19 @@
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N7" t="s">
         <v>31</v>
@@ -1503,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1512,12 +1461,12 @@
         <v>28</v>
       </c>
       <c r="AA7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1529,7 +1478,7 @@
         <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F8" t="s">
         <v>30</v>
@@ -1538,19 +1487,19 @@
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>201</v>
+      </c>
+      <c r="L8" t="s">
         <v>33</v>
       </c>
-      <c r="J8" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" t="s">
-        <v>34</v>
-      </c>
       <c r="M8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N8" t="s">
         <v>31</v>
@@ -1562,7 +1511,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1571,24 +1520,24 @@
         <v>28</v>
       </c>
       <c r="AA8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
         <v>30</v>
@@ -1597,19 +1546,20 @@
         <v>31</v>
       </c>
       <c r="H9" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I9" t="s">
-        <v>33</v>
-      </c>
-      <c r="J9" t="s">
-        <v>55</v>
+        <v>32</v>
+      </c>
+      <c r="J9" t="str">
+        <f>H9</f>
+        <v>VGC</v>
       </c>
       <c r="L9" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N9" t="s">
         <v>31</v>
@@ -1621,7 +1571,7 @@
         <v>0</v>
       </c>
       <c r="S9" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="T9">
         <v>9</v>
@@ -1630,24 +1580,24 @@
         <v>28</v>
       </c>
       <c r="AA9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>205</v>
+        <v>167</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F10" t="s">
         <v>30</v>
@@ -1656,19 +1606,19 @@
         <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>186</v>
+      </c>
+      <c r="L10" t="s">
         <v>33</v>
       </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>34</v>
-      </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N10" t="s">
         <v>31</v>
@@ -1680,7 +1630,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1689,12 +1639,12 @@
         <v>28</v>
       </c>
       <c r="AA10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
         <v>26</v>
@@ -1706,7 +1656,7 @@
         <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F11" t="s">
         <v>30</v>
@@ -1715,19 +1665,19 @@
         <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L11" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N11" t="s">
         <v>31</v>
@@ -1739,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1748,12 +1698,12 @@
         <v>28</v>
       </c>
       <c r="AA11" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
@@ -1765,7 +1715,7 @@
         <v>28</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F12" t="s">
         <v>30</v>
@@ -1774,19 +1724,19 @@
         <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="I12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="L12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N12" t="s">
         <v>31</v>
@@ -1798,7 +1748,7 @@
         <v>0</v>
       </c>
       <c r="S12" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1807,25 +1757,25 @@
         <v>28</v>
       </c>
       <c r="AA12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" t="s">
         <v>41</v>
       </c>
-      <c r="B13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" t="s">
-        <v>42</v>
-      </c>
       <c r="F13" t="s">
         <v>30</v>
       </c>
@@ -1833,19 +1783,19 @@
         <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M13" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N13" t="s">
         <v>31</v>
@@ -1857,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="S13" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1866,24 +1816,24 @@
         <v>28</v>
       </c>
       <c r="AA13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F14" t="s">
         <v>30</v>
@@ -1892,19 +1842,19 @@
         <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="I14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>67</v>
+        <v>198</v>
       </c>
       <c r="L14" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N14" t="s">
         <v>31</v>
@@ -1916,7 +1866,7 @@
         <v>0</v>
       </c>
       <c r="S14" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="T14">
         <v>9</v>
@@ -1925,24 +1875,24 @@
         <v>28</v>
       </c>
       <c r="AA14" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="C15" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F15" t="s">
         <v>30</v>
@@ -1951,19 +1901,19 @@
         <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="I15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="L15" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N15" t="s">
         <v>31</v>
@@ -1975,7 +1925,7 @@
         <v>0</v>
       </c>
       <c r="S15" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1984,24 +1934,24 @@
         <v>28</v>
       </c>
       <c r="AA15" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F16" t="s">
         <v>30</v>
@@ -2010,19 +1960,19 @@
         <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>71</v>
+        <v>192</v>
       </c>
       <c r="L16" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N16" t="s">
         <v>31</v>
@@ -2034,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="T16">
         <v>9</v>
@@ -2043,24 +1993,24 @@
         <v>28</v>
       </c>
       <c r="AA16" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="C17" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D17" t="s">
         <v>28</v>
       </c>
       <c r="E17" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F17" t="s">
         <v>30</v>
@@ -2069,19 +2019,19 @@
         <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N17" t="s">
         <v>31</v>
@@ -2093,7 +2043,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="T17">
         <v>9</v>
@@ -2102,24 +2052,24 @@
         <v>28</v>
       </c>
       <c r="AA17" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="C18" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
         <v>30</v>
@@ -2128,19 +2078,19 @@
         <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L18" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N18" t="s">
         <v>31</v>
@@ -2152,7 +2102,7 @@
         <v>0</v>
       </c>
       <c r="S18" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="T18">
         <v>9</v>
@@ -2161,24 +2111,24 @@
         <v>28</v>
       </c>
       <c r="AA18" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="C19" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
         <v>30</v>
@@ -2187,19 +2137,19 @@
         <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>53</v>
+        <v>201</v>
       </c>
       <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s">
         <v>33</v>
       </c>
-      <c r="J19" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" t="s">
-        <v>34</v>
-      </c>
       <c r="M19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N19" t="s">
         <v>31</v>
@@ -2211,7 +2161,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2220,24 +2170,24 @@
         <v>28</v>
       </c>
       <c r="AA19" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C20" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
         <v>28</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F20" t="s">
         <v>30</v>
@@ -2246,19 +2196,19 @@
         <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="I20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>190</v>
       </c>
       <c r="L20" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N20" t="s">
         <v>31</v>
@@ -2270,7 +2220,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="T20">
         <v>6</v>
@@ -2279,24 +2229,24 @@
         <v>28</v>
       </c>
       <c r="AA20" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D21" t="s">
         <v>28</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F21" t="s">
         <v>30</v>
@@ -2305,19 +2255,19 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>193</v>
+      </c>
+      <c r="L21" t="s">
         <v>33</v>
       </c>
-      <c r="J21" t="s">
-        <v>82</v>
-      </c>
-      <c r="L21" t="s">
-        <v>34</v>
-      </c>
       <c r="M21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N21" t="s">
         <v>31</v>
@@ -2329,7 +2279,7 @@
         <v>0</v>
       </c>
       <c r="S21" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="T21">
         <v>9</v>
@@ -2338,24 +2288,24 @@
         <v>28</v>
       </c>
       <c r="AA21" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="C22" t="s">
-        <v>208</v>
+        <v>170</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F22" t="s">
         <v>30</v>
@@ -2364,19 +2314,19 @@
         <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N22" t="s">
         <v>31</v>
@@ -2388,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2397,24 +2347,24 @@
         <v>28</v>
       </c>
       <c r="AA22" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="C23" t="s">
-        <v>210</v>
+        <v>172</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F23" t="s">
         <v>30</v>
@@ -2423,19 +2373,19 @@
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="I23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="L23" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N23" t="s">
         <v>31</v>
@@ -2447,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2456,24 +2406,24 @@
         <v>28</v>
       </c>
       <c r="AA23" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
       </c>
       <c r="E24" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
         <v>30</v>
@@ -2482,19 +2432,19 @@
         <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="I24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="L24" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N24" t="s">
         <v>31</v>
@@ -2506,7 +2456,7 @@
         <v>0</v>
       </c>
       <c r="S24" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2515,24 +2465,24 @@
         <v>28</v>
       </c>
       <c r="AA24" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>171</v>
       </c>
       <c r="C25" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D25" t="s">
         <v>28</v>
       </c>
       <c r="E25" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F25" t="s">
         <v>30</v>
@@ -2541,19 +2491,19 @@
         <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="I25" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N25" t="s">
         <v>31</v>
@@ -2565,7 +2515,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="T25">
         <v>7</v>
@@ -2574,24 +2524,24 @@
         <v>28</v>
       </c>
       <c r="AA25" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B26" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
       </c>
       <c r="E26" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
         <v>30</v>
@@ -2600,57 +2550,57 @@
         <v>31</v>
       </c>
       <c r="H26" t="s">
+        <v>191</v>
+      </c>
+      <c r="I26" t="s">
+        <v>32</v>
+      </c>
+      <c r="J26" t="s">
+        <v>191</v>
+      </c>
+      <c r="L26" t="s">
+        <v>43</v>
+      </c>
+      <c r="M26" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" t="s">
+        <v>31</v>
+      </c>
+      <c r="P26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>0</v>
+      </c>
+      <c r="S26" t="s">
+        <v>78</v>
+      </c>
+      <c r="T26">
+        <v>9</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA26" t="s">
         <v>75</v>
-      </c>
-      <c r="I26" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" t="s">
-        <v>75</v>
-      </c>
-      <c r="L26" t="s">
-        <v>46</v>
-      </c>
-      <c r="M26" t="s">
-        <v>35</v>
-      </c>
-      <c r="N26" t="s">
-        <v>31</v>
-      </c>
-      <c r="P26">
-        <v>1</v>
-      </c>
-      <c r="R26">
-        <v>0</v>
-      </c>
-      <c r="S26" t="s">
-        <v>95</v>
-      </c>
-      <c r="T26">
-        <v>9</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA26" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="C27" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="D27" t="s">
         <v>28</v>
       </c>
       <c r="E27" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F27" t="s">
         <v>30</v>
@@ -2659,19 +2609,19 @@
         <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="L27" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N27" t="s">
         <v>31</v>
@@ -2683,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="S27" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2692,24 +2642,24 @@
         <v>28</v>
       </c>
       <c r="AA27" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B28" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D28" t="s">
         <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F28" t="s">
         <v>30</v>
@@ -2718,19 +2668,19 @@
         <v>31</v>
       </c>
       <c r="H28" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="I28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>92</v>
+        <v>188</v>
       </c>
       <c r="L28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N28" t="s">
         <v>31</v>
@@ -2742,7 +2692,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2751,24 +2701,24 @@
         <v>28</v>
       </c>
       <c r="AA28" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="C29" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
       </c>
       <c r="E29" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
         <v>30</v>
@@ -2777,19 +2727,19 @@
         <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L29" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M29" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N29" t="s">
         <v>31</v>
@@ -2801,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="S29" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="T29">
         <v>9</v>
@@ -2810,24 +2760,24 @@
         <v>28</v>
       </c>
       <c r="AA29" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="D30" t="s">
         <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F30" t="s">
         <v>30</v>
@@ -2836,19 +2786,19 @@
         <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M30" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N30" t="s">
         <v>31</v>
@@ -2860,7 +2810,7 @@
         <v>0</v>
       </c>
       <c r="S30" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2869,24 +2819,24 @@
         <v>28</v>
       </c>
       <c r="AA30" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>214</v>
+        <v>176</v>
       </c>
       <c r="D31" t="s">
         <v>28</v>
       </c>
       <c r="E31" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
         <v>30</v>
@@ -2895,19 +2845,19 @@
         <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L31" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M31" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N31" t="s">
         <v>31</v>
@@ -2919,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="S31" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="T31">
         <v>9</v>
@@ -2928,24 +2878,24 @@
         <v>28</v>
       </c>
       <c r="AA31" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="C32" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="D32" t="s">
         <v>28</v>
       </c>
       <c r="E32" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F32" t="s">
         <v>30</v>
@@ -2954,19 +2904,19 @@
         <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="I32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="L32" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N32" t="s">
         <v>31</v>
@@ -2978,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -2987,24 +2937,24 @@
         <v>28</v>
       </c>
       <c r="AA32" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="B33" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="C33" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="D33" t="s">
         <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F33" t="s">
         <v>30</v>
@@ -3013,19 +2963,19 @@
         <v>31</v>
       </c>
       <c r="H33" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="I33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="L33" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M33" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N33" t="s">
         <v>31</v>
@@ -3037,7 +2987,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3046,24 +2996,24 @@
         <v>28</v>
       </c>
       <c r="AA33" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="B34" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C34" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F34" t="s">
         <v>30</v>
@@ -3072,19 +3022,19 @@
         <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="I34" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="L34" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M34" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N34" t="s">
         <v>31</v>
@@ -3096,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3105,15 +3055,15 @@
         <v>28</v>
       </c>
       <c r="AA34" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="B35" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
@@ -3122,7 +3072,7 @@
         <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F35" t="s">
         <v>30</v>
@@ -3131,32 +3081,32 @@
         <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="I35" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="L35" t="s">
+        <v>43</v>
+      </c>
+      <c r="M35" t="s">
+        <v>34</v>
+      </c>
+      <c r="N35" t="s">
+        <v>31</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <v>0</v>
+      </c>
+      <c r="S35" t="s">
         <v>46</v>
       </c>
-      <c r="M35" t="s">
-        <v>35</v>
-      </c>
-      <c r="N35" t="s">
-        <v>31</v>
-      </c>
-      <c r="P35">
-        <v>1</v>
-      </c>
-      <c r="R35">
-        <v>0</v>
-      </c>
-      <c r="S35" t="s">
-        <v>50</v>
-      </c>
       <c r="T35">
         <v>9</v>
       </c>
@@ -3164,24 +3114,24 @@
         <v>28</v>
       </c>
       <c r="AA35" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="B36" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="C36" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
         <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F36" t="s">
         <v>30</v>
@@ -3190,19 +3140,19 @@
         <v>31</v>
       </c>
       <c r="H36" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="I36" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="L36" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M36" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N36" t="s">
         <v>31</v>
@@ -3214,7 +3164,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3223,24 +3173,24 @@
         <v>28</v>
       </c>
       <c r="AA36" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="B37" t="s">
-        <v>207</v>
+        <v>169</v>
       </c>
       <c r="C37" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
       </c>
       <c r="E37" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F37" t="s">
         <v>30</v>
@@ -3249,19 +3199,19 @@
         <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="I37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="L37" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M37" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N37" t="s">
         <v>31</v>
@@ -3273,7 +3223,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3282,24 +3232,24 @@
         <v>28</v>
       </c>
       <c r="AA37" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="C38" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F38" t="s">
         <v>30</v>
@@ -3308,19 +3258,19 @@
         <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="I38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>105</v>
+        <v>189</v>
       </c>
       <c r="L38" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M38" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N38" t="s">
         <v>31</v>
@@ -3332,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="s">
-        <v>212</v>
+        <v>174</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3341,24 +3291,24 @@
         <v>28</v>
       </c>
       <c r="AA38" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="C39" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
       </c>
       <c r="E39" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F39" t="s">
         <v>30</v>
@@ -3367,19 +3317,19 @@
         <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="I39" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J39" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="L39" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N39" t="s">
         <v>31</v>
@@ -3391,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -3400,24 +3350,24 @@
         <v>28</v>
       </c>
       <c r="AA39" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="B40" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
-        <v>204</v>
+        <v>166</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
       </c>
       <c r="E40" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F40" t="s">
         <v>30</v>
@@ -3426,19 +3376,19 @@
         <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I40" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J40" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L40" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M40" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N40" t="s">
         <v>31</v>
@@ -3450,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3459,24 +3409,24 @@
         <v>28</v>
       </c>
       <c r="AA40" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>206</v>
+        <v>168</v>
       </c>
       <c r="B41" t="s">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
       </c>
       <c r="E41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
         <v>30</v>
@@ -3485,19 +3435,19 @@
         <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L41" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N41" t="s">
         <v>31</v>
@@ -3509,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -3518,83 +3468,83 @@
         <v>28</v>
       </c>
       <c r="AA41" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B42" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="C42" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
       </c>
       <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" t="s">
+        <v>31</v>
+      </c>
+      <c r="H42" t="s">
+        <v>196</v>
+      </c>
+      <c r="I42" t="s">
+        <v>32</v>
+      </c>
+      <c r="J42" t="s">
+        <v>196</v>
+      </c>
+      <c r="L42" t="s">
+        <v>43</v>
+      </c>
+      <c r="M42" t="s">
+        <v>34</v>
+      </c>
+      <c r="N42" t="s">
+        <v>31</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42" t="s">
+        <v>98</v>
+      </c>
+      <c r="T42">
+        <v>9</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA42" t="s">
         <v>99</v>
-      </c>
-      <c r="F42" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" t="s">
-        <v>31</v>
-      </c>
-      <c r="H42" t="s">
-        <v>85</v>
-      </c>
-      <c r="I42" t="s">
-        <v>33</v>
-      </c>
-      <c r="J42" t="s">
-        <v>85</v>
-      </c>
-      <c r="L42" t="s">
-        <v>46</v>
-      </c>
-      <c r="M42" t="s">
-        <v>35</v>
-      </c>
-      <c r="N42" t="s">
-        <v>31</v>
-      </c>
-      <c r="P42">
-        <v>1</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42" t="s">
-        <v>122</v>
-      </c>
-      <c r="T42">
-        <v>9</v>
-      </c>
-      <c r="Z42" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA42" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F43" t="s">
         <v>30</v>
@@ -3603,19 +3553,19 @@
         <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I43" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L43" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M43" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N43" t="s">
         <v>31</v>
@@ -3627,7 +3577,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="T43">
         <v>9</v>
@@ -3636,83 +3586,83 @@
         <v>28</v>
       </c>
       <c r="AA43" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C44" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="D44" t="s">
         <v>28</v>
       </c>
       <c r="E44" t="s">
+        <v>81</v>
+      </c>
+      <c r="F44" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>31</v>
+      </c>
+      <c r="H44" t="s">
+        <v>187</v>
+      </c>
+      <c r="I44" t="s">
+        <v>32</v>
+      </c>
+      <c r="J44" t="s">
+        <v>187</v>
+      </c>
+      <c r="L44" t="s">
+        <v>43</v>
+      </c>
+      <c r="M44" t="s">
+        <v>34</v>
+      </c>
+      <c r="N44" t="s">
+        <v>31</v>
+      </c>
+      <c r="P44">
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44" t="s">
+        <v>104</v>
+      </c>
+      <c r="T44">
+        <v>9</v>
+      </c>
+      <c r="Z44" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA44" t="s">
         <v>99</v>
-      </c>
-      <c r="F44" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44" t="s">
-        <v>45</v>
-      </c>
-      <c r="I44" t="s">
-        <v>33</v>
-      </c>
-      <c r="J44" t="s">
-        <v>45</v>
-      </c>
-      <c r="L44" t="s">
-        <v>46</v>
-      </c>
-      <c r="M44" t="s">
-        <v>35</v>
-      </c>
-      <c r="N44" t="s">
-        <v>31</v>
-      </c>
-      <c r="P44">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>0</v>
-      </c>
-      <c r="S44" t="s">
-        <v>128</v>
-      </c>
-      <c r="T44">
-        <v>9</v>
-      </c>
-      <c r="Z44" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA44" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="C45" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
       </c>
       <c r="E45" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
@@ -3721,19 +3671,19 @@
         <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L45" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M45" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N45" t="s">
         <v>31</v>
@@ -3745,7 +3695,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="T45">
         <v>9</v>
@@ -3754,24 +3704,24 @@
         <v>28</v>
       </c>
       <c r="AA45" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="C46" t="s">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="D46" t="s">
         <v>28</v>
       </c>
       <c r="E46" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F46" t="s">
         <v>30</v>
@@ -3780,19 +3730,19 @@
         <v>31</v>
       </c>
       <c r="H46" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I46" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L46" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N46" t="s">
         <v>31</v>
@@ -3804,7 +3754,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -3813,24 +3763,24 @@
         <v>28</v>
       </c>
       <c r="AA46" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C47" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D47" t="s">
         <v>28</v>
       </c>
       <c r="E47" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F47" t="s">
         <v>30</v>
@@ -3839,19 +3789,19 @@
         <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L47" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N47" t="s">
         <v>31</v>
@@ -3863,7 +3813,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="T47">
         <v>9</v>
@@ -3872,83 +3822,83 @@
         <v>28</v>
       </c>
       <c r="AA47" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>213</v>
+        <v>175</v>
       </c>
       <c r="D48" t="s">
         <v>28</v>
       </c>
       <c r="E48" t="s">
+        <v>81</v>
+      </c>
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>31</v>
+      </c>
+      <c r="H48" t="s">
+        <v>200</v>
+      </c>
+      <c r="I48" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" t="s">
+        <v>200</v>
+      </c>
+      <c r="L48" t="s">
+        <v>33</v>
+      </c>
+      <c r="M48" t="s">
+        <v>34</v>
+      </c>
+      <c r="N48" t="s">
+        <v>31</v>
+      </c>
+      <c r="P48">
+        <v>1</v>
+      </c>
+      <c r="R48">
+        <v>0</v>
+      </c>
+      <c r="S48" t="s">
+        <v>108</v>
+      </c>
+      <c r="T48">
+        <v>9</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA48" t="s">
         <v>99</v>
-      </c>
-      <c r="F48" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" t="s">
-        <v>31</v>
-      </c>
-      <c r="H48" t="s">
-        <v>132</v>
-      </c>
-      <c r="I48" t="s">
-        <v>33</v>
-      </c>
-      <c r="J48" t="s">
-        <v>132</v>
-      </c>
-      <c r="L48" t="s">
-        <v>34</v>
-      </c>
-      <c r="M48" t="s">
-        <v>35</v>
-      </c>
-      <c r="N48" t="s">
-        <v>31</v>
-      </c>
-      <c r="P48">
-        <v>1</v>
-      </c>
-      <c r="R48">
-        <v>0</v>
-      </c>
-      <c r="S48" t="s">
-        <v>133</v>
-      </c>
-      <c r="T48">
-        <v>9</v>
-      </c>
-      <c r="Z48" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA48" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="B49" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C49" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
         <v>28</v>
       </c>
       <c r="E49" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F49" t="s">
         <v>30</v>
@@ -3957,19 +3907,19 @@
         <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="I49" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="L49" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M49" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N49" t="s">
         <v>31</v>
@@ -3981,7 +3931,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="T49">
         <v>9</v>
@@ -3990,24 +3940,24 @@
         <v>28</v>
       </c>
       <c r="AA49" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="C50" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="D50" t="s">
         <v>28</v>
       </c>
       <c r="E50" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
@@ -4016,19 +3966,19 @@
         <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I50" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J50" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L50" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N50" t="s">
         <v>31</v>
@@ -4040,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="T50">
         <v>9</v>
@@ -4049,24 +3999,24 @@
         <v>28</v>
       </c>
       <c r="AA50" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="C51" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="D51" t="s">
         <v>28</v>
       </c>
       <c r="E51" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F51" t="s">
         <v>30</v>
@@ -4075,19 +4025,19 @@
         <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="I51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J51" t="s">
-        <v>49</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N51" t="s">
         <v>31</v>
@@ -4099,7 +4049,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="T51">
         <v>9</v>
@@ -4108,24 +4058,24 @@
         <v>28</v>
       </c>
       <c r="AA51" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="B52" t="s">
-        <v>216</v>
+        <v>178</v>
       </c>
       <c r="C52" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="D52" t="s">
         <v>28</v>
       </c>
       <c r="E52" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F52" t="s">
         <v>30</v>
@@ -4134,19 +4084,19 @@
         <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="I52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J52" t="s">
-        <v>144</v>
+        <v>204</v>
       </c>
       <c r="L52" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M52" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N52" t="s">
         <v>31</v>
@@ -4158,7 +4108,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="T52">
         <v>9</v>
@@ -4167,24 +4117,24 @@
         <v>28</v>
       </c>
       <c r="AA52" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="B53" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="C53" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="D53" t="s">
         <v>28</v>
       </c>
       <c r="E53" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
@@ -4193,19 +4143,19 @@
         <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="I53" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J53" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="L53" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N53" t="s">
         <v>31</v>
@@ -4217,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="T53">
         <v>9</v>
@@ -4226,24 +4176,24 @@
         <v>28</v>
       </c>
       <c r="AA53" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="B54" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="C54" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
@@ -4252,19 +4202,19 @@
         <v>31</v>
       </c>
       <c r="H54" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="I54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J54" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="L54" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M54" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N54" t="s">
         <v>31</v>
@@ -4276,7 +4226,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="s">
-        <v>149</v>
+        <v>118</v>
       </c>
       <c r="T54">
         <v>9</v>
@@ -4285,24 +4235,24 @@
         <v>28</v>
       </c>
       <c r="AA54" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="B55" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="C55" t="s">
-        <v>219</v>
+        <v>181</v>
       </c>
       <c r="D55" t="s">
         <v>28</v>
       </c>
       <c r="E55" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F55" t="s">
         <v>30</v>
@@ -4311,19 +4261,19 @@
         <v>31</v>
       </c>
       <c r="H55" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="I55" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J55" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="L55" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M55" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N55" t="s">
         <v>31</v>
@@ -4335,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="T55">
         <v>9</v>
@@ -4344,24 +4294,24 @@
         <v>28</v>
       </c>
       <c r="AA55" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="C56" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
       <c r="D56" t="s">
         <v>28</v>
       </c>
       <c r="E56" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F56" t="s">
         <v>30</v>
@@ -4370,19 +4320,19 @@
         <v>31</v>
       </c>
       <c r="H56" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="I56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J56" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="L56" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M56" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N56" t="s">
         <v>31</v>
@@ -4394,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="T56">
         <v>9</v>
@@ -4403,24 +4353,24 @@
         <v>28</v>
       </c>
       <c r="AA56" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="B57" t="s">
-        <v>223</v>
+        <v>185</v>
       </c>
       <c r="C57" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="D57" t="s">
         <v>28</v>
       </c>
       <c r="E57" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F57" t="s">
         <v>30</v>
@@ -4429,19 +4379,19 @@
         <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="I57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J57" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="L57" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M57" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N57" t="s">
         <v>31</v>
@@ -4453,7 +4403,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="T57">
         <v>9</v>
@@ -4462,24 +4412,24 @@
         <v>28</v>
       </c>
       <c r="AA57" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="B58" t="s">
-        <v>217</v>
+        <v>179</v>
       </c>
       <c r="C58" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="D58" t="s">
         <v>28</v>
       </c>
       <c r="E58" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
         <v>30</v>
@@ -4488,19 +4438,19 @@
         <v>31</v>
       </c>
       <c r="H58" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="I58" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J58" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="L58" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M58" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N58" t="s">
         <v>31</v>
@@ -4512,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="T58">
         <v>9</v>
@@ -4521,24 +4471,24 @@
         <v>28</v>
       </c>
       <c r="AA58" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="B59" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="D59" t="s">
         <v>28</v>
       </c>
       <c r="E59" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F59" t="s">
         <v>30</v>
@@ -4547,19 +4497,19 @@
         <v>31</v>
       </c>
       <c r="H59" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="I59" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J59" t="s">
-        <v>148</v>
+        <v>50</v>
       </c>
       <c r="L59" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M59" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N59" t="s">
         <v>31</v>
@@ -4571,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="T59">
         <v>9</v>
@@ -4580,24 +4530,24 @@
         <v>28</v>
       </c>
       <c r="AA59" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="B60" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="C60" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="D60" t="s">
         <v>28</v>
       </c>
       <c r="E60" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F60" t="s">
         <v>30</v>
@@ -4606,19 +4556,19 @@
         <v>31</v>
       </c>
       <c r="H60" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="I60" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J60" t="s">
-        <v>159</v>
+        <v>187</v>
       </c>
       <c r="L60" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N60" t="s">
         <v>31</v>
@@ -4630,7 +4580,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="s">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="T60">
         <v>2</v>
@@ -4639,24 +4589,24 @@
         <v>28</v>
       </c>
       <c r="AA60" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C61" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="D61" t="s">
         <v>28</v>
       </c>
       <c r="E61" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F61" t="s">
         <v>30</v>
@@ -4665,19 +4615,19 @@
         <v>31</v>
       </c>
       <c r="H61" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="I61" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J61" t="s">
-        <v>162</v>
+        <v>197</v>
       </c>
       <c r="L61" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M61" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N61" t="s">
         <v>31</v>
@@ -4689,7 +4639,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="T61">
         <v>9</v>
@@ -4698,24 +4648,24 @@
         <v>28</v>
       </c>
       <c r="AA61" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B62" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="C62" t="s">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="D62" t="s">
         <v>28</v>
       </c>
       <c r="E62" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F62" t="s">
         <v>30</v>
@@ -4724,19 +4674,19 @@
         <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J62" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L62" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M62" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N62" t="s">
         <v>31</v>
@@ -4748,7 +4698,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="s">
-        <v>164</v>
+        <v>131</v>
       </c>
       <c r="T62">
         <v>9</v>
@@ -4757,24 +4707,24 @@
         <v>28</v>
       </c>
       <c r="AA62" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="B63" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="C63" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D63" t="s">
         <v>28</v>
       </c>
       <c r="E63" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F63" t="s">
         <v>30</v>
@@ -4783,19 +4733,19 @@
         <v>31</v>
       </c>
       <c r="H63" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I63" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J63" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L63" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M63" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N63" t="s">
         <v>31</v>
@@ -4807,7 +4757,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="s">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="T63">
         <v>9</v>
@@ -4816,24 +4766,24 @@
         <v>28</v>
       </c>
       <c r="AA63" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B64" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C64" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D64" t="s">
         <v>28</v>
       </c>
       <c r="E64" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F64" t="s">
         <v>30</v>
@@ -4842,19 +4792,19 @@
         <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I64" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J64" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L64" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M64" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N64" t="s">
         <v>31</v>
@@ -4866,7 +4816,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="s">
-        <v>166</v>
+        <v>133</v>
       </c>
       <c r="T64">
         <v>9</v>
@@ -4875,24 +4825,24 @@
         <v>28</v>
       </c>
       <c r="AA64" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B65" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="C65" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="D65" t="s">
         <v>28</v>
       </c>
       <c r="E65" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
@@ -4901,19 +4851,19 @@
         <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I65" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J65" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L65" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M65" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N65" t="s">
         <v>31</v>
@@ -4925,7 +4875,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="s">
-        <v>167</v>
+        <v>134</v>
       </c>
       <c r="T65">
         <v>9</v>
@@ -4934,24 +4884,24 @@
         <v>28</v>
       </c>
       <c r="AA65" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="B66" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>183</v>
       </c>
       <c r="D66" t="s">
         <v>28</v>
       </c>
       <c r="E66" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="F66" t="s">
         <v>30</v>
@@ -4960,19 +4910,19 @@
         <v>31</v>
       </c>
       <c r="H66" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I66" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J66" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L66" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M66" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N66" t="s">
         <v>31</v>
@@ -4984,7 +4934,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="s">
-        <v>169</v>
+        <v>136</v>
       </c>
       <c r="T66">
         <v>9</v>
@@ -4993,24 +4943,24 @@
         <v>28</v>
       </c>
       <c r="AA66" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="B67" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="C67" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="D67" t="s">
         <v>28</v>
       </c>
       <c r="E67" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F67" t="s">
         <v>30</v>
@@ -5019,19 +4969,19 @@
         <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="I67" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J67" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="L67" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N67" t="s">
         <v>31</v>
@@ -5043,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="S67" t="s">
-        <v>171</v>
+        <v>137</v>
       </c>
       <c r="T67">
         <v>9</v>
@@ -5052,24 +5002,24 @@
         <v>28</v>
       </c>
       <c r="AA67" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="B68" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="D68" t="s">
         <v>28</v>
       </c>
       <c r="E68" t="s">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
@@ -5078,19 +5028,19 @@
         <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="I68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J68" t="s">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="L68" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M68" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N68" t="s">
         <v>31</v>
@@ -5102,7 +5052,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="T68">
         <v>9</v>
@@ -5111,24 +5061,24 @@
         <v>28</v>
       </c>
       <c r="AA68" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B69" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C69" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="D69" t="s">
         <v>28</v>
       </c>
       <c r="E69" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="F69" t="s">
         <v>30</v>
@@ -5137,19 +5087,19 @@
         <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I69" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J69" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L69" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M69" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N69" t="s">
         <v>31</v>
@@ -5161,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="s">
-        <v>175</v>
+        <v>141</v>
       </c>
       <c r="T69">
         <v>9</v>
@@ -5170,24 +5120,24 @@
         <v>28</v>
       </c>
       <c r="AA69" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B70" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C70" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D70" t="s">
         <v>28</v>
       </c>
       <c r="E70" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F70" t="s">
         <v>30</v>
@@ -5196,19 +5146,19 @@
         <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="I70" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J70" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="L70" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M70" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N70" t="s">
         <v>31</v>
@@ -5220,7 +5170,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="s">
-        <v>178</v>
+        <v>144</v>
       </c>
       <c r="T70">
         <v>9</v>
@@ -5229,24 +5179,24 @@
         <v>28</v>
       </c>
       <c r="AA70" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="B71" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C71" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="D71" t="s">
         <v>28</v>
       </c>
       <c r="E71" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F71" t="s">
         <v>30</v>
@@ -5255,19 +5205,19 @@
         <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="I71" t="s">
+        <v>32</v>
+      </c>
+      <c r="J71" t="s">
+        <v>186</v>
+      </c>
+      <c r="L71" t="s">
         <v>33</v>
       </c>
-      <c r="J71" t="s">
-        <v>32</v>
-      </c>
-      <c r="L71" t="s">
-        <v>34</v>
-      </c>
       <c r="M71" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N71" t="s">
         <v>31</v>
@@ -5279,7 +5229,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="s">
-        <v>180</v>
+        <v>146</v>
       </c>
       <c r="T71">
         <v>9</v>
@@ -5288,24 +5238,24 @@
         <v>28</v>
       </c>
       <c r="AA71" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C72" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="D72" t="s">
         <v>28</v>
       </c>
       <c r="E72" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="F72" t="s">
         <v>30</v>
@@ -5314,19 +5264,19 @@
         <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="I72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J72" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="L72" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M72" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N72" t="s">
         <v>31</v>
@@ -5338,7 +5288,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="s">
-        <v>183</v>
+        <v>148</v>
       </c>
       <c r="T72">
         <v>9</v>
@@ -5347,24 +5297,24 @@
         <v>28</v>
       </c>
       <c r="AA72" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="B73" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C73" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="D73" t="s">
         <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F73" t="s">
         <v>30</v>
@@ -5373,19 +5323,19 @@
         <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="I73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J73" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="L73" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M73" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N73" t="s">
         <v>31</v>
@@ -5397,7 +5347,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="s">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="T73">
         <v>9</v>
@@ -5406,24 +5356,24 @@
         <v>28</v>
       </c>
       <c r="AA73" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="B74" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="D74" t="s">
         <v>28</v>
       </c>
       <c r="E74" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F74" t="s">
         <v>30</v>
@@ -5432,19 +5382,19 @@
         <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="I74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J74" t="s">
-        <v>186</v>
+        <v>205</v>
       </c>
       <c r="L74" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N74" t="s">
         <v>31</v>
@@ -5456,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="S74" t="s">
-        <v>187</v>
+        <v>150</v>
       </c>
       <c r="T74">
         <v>9</v>
@@ -5465,24 +5415,24 @@
         <v>28</v>
       </c>
       <c r="AA74" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="D75" t="s">
         <v>28</v>
       </c>
       <c r="E75" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F75" t="s">
         <v>30</v>
@@ -5491,19 +5441,19 @@
         <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="I75" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J75" t="s">
-        <v>45</v>
+        <v>187</v>
       </c>
       <c r="L75" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M75" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N75" t="s">
         <v>31</v>
@@ -5515,7 +5465,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="s">
-        <v>188</v>
+        <v>151</v>
       </c>
       <c r="T75">
         <v>9</v>
@@ -5524,24 +5474,24 @@
         <v>28</v>
       </c>
       <c r="AA75" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="B76" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C76" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="D76" t="s">
         <v>28</v>
       </c>
       <c r="E76" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F76" t="s">
         <v>30</v>
@@ -5550,19 +5500,19 @@
         <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="I76" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J76" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L76" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M76" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N76" t="s">
         <v>31</v>
@@ -5574,7 +5524,7 @@
         <v>0</v>
       </c>
       <c r="S76" t="s">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="T76">
         <v>8</v>
@@ -5583,24 +5533,24 @@
         <v>28</v>
       </c>
       <c r="AA76" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="B77" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C77" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D77" t="s">
         <v>28</v>
       </c>
       <c r="E77" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F77" t="s">
         <v>30</v>
@@ -5609,19 +5559,19 @@
         <v>31</v>
       </c>
       <c r="H77" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="I77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J77" t="s">
-        <v>114</v>
+        <v>194</v>
       </c>
       <c r="L77" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="M77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N77" t="s">
         <v>31</v>
@@ -5633,7 +5583,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="s">
-        <v>191</v>
+        <v>153</v>
       </c>
       <c r="T77">
         <v>9</v>
@@ -5642,24 +5592,24 @@
         <v>28</v>
       </c>
       <c r="AA77" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="B78" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="C78" t="s">
-        <v>222</v>
+        <v>184</v>
       </c>
       <c r="D78" t="s">
         <v>28</v>
       </c>
       <c r="E78" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="F78" t="s">
         <v>30</v>
@@ -5668,19 +5618,19 @@
         <v>31</v>
       </c>
       <c r="H78" t="s">
-        <v>32</v>
+        <v>186</v>
       </c>
       <c r="I78" t="s">
+        <v>32</v>
+      </c>
+      <c r="J78" t="s">
+        <v>186</v>
+      </c>
+      <c r="L78" t="s">
         <v>33</v>
       </c>
-      <c r="J78" t="s">
-        <v>32</v>
-      </c>
-      <c r="L78" t="s">
-        <v>34</v>
-      </c>
       <c r="M78" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="N78" t="s">
         <v>31</v>
@@ -5692,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="S78" t="s">
-        <v>192</v>
+        <v>154</v>
       </c>
       <c r="T78">
         <v>9</v>
@@ -5701,7 +5651,7 @@
         <v>28</v>
       </c>
       <c r="AA78" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -5721,15 +5671,15 @@
         <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>193</v>
+        <v>155</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>26</v>
@@ -5740,7 +5690,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B3" t="s">
         <v>27</v>
@@ -5751,10 +5701,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>167</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -5762,10 +5712,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5">
         <v>2</v>
@@ -5773,10 +5723,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -5784,10 +5734,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B7" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -5795,10 +5745,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>172</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -5806,10 +5756,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -5817,10 +5767,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -5828,10 +5778,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -5839,18 +5789,18 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>176</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -5858,10 +5808,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B14" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -5869,10 +5819,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -5880,10 +5830,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>108</v>
+        <v>173</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -5891,18 +5841,18 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B17" t="s">
-        <v>112</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B18" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -5910,10 +5860,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5921,10 +5871,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B20" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -5932,26 +5882,26 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="B21" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B22" t="s">
-        <v>134</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B23" t="s">
-        <v>135</v>
+        <v>181</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -5959,10 +5909,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B24" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -5970,10 +5920,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>180</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -5981,10 +5931,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B26" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -5992,10 +5942,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B27" t="s">
-        <v>155</v>
+        <v>124</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -6003,10 +5953,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -6014,18 +5964,18 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>157</v>
+        <v>126</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -6033,10 +5983,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C31">
         <v>4</v>
@@ -6044,10 +5994,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="B32" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6055,10 +6005,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="B33" t="s">
-        <v>179</v>
+        <v>145</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -6085,93 +6035,93 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>195</v>
+        <v>157</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>196</v>
+        <v>158</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
         <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="F2" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B3" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="E3" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="F3" t="s">
-        <v>200</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B4" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F4" t="s">
-        <v>201</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>176</v>
+        <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>140</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D5" t="s">
-        <v>202</v>
+        <v>164</v>
       </c>
       <c r="E5" t="s">
-        <v>181</v>
+        <v>147</v>
       </c>
       <c r="F5" t="s">
-        <v>203</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/data/guerra_mafias_3.xlsx
+++ b/data/guerra_mafias_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\power bi\webhook\Produccion\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3998FB2-7332-4974-BC11-7DACEF006EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{871827B2-E8C9-49C9-9D2E-A933659ED72D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Batallas" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1355" uniqueCount="203">
   <si>
     <t>player1</t>
   </si>
@@ -293,9 +293,6 @@
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2701946499-8gpac1h4y6qgbcxyyx1t1dampiii9a6pw</t>
   </si>
   <si>
-    <t>Josar</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen8vgc2021-2701703506</t>
   </si>
   <si>
@@ -311,18 +308,12 @@
     <t>https://replay.pokemonshowdown.com/gen9monotyperandombattle-2701685590</t>
   </si>
   <si>
-    <t>Arnaenaed ∾</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen8vgc2021-2700127756</t>
   </si>
   <si>
     <t>https://replay.pokemonshowdown.com/gen9nationaldexmonotype-2697860912</t>
   </si>
   <si>
-    <t>zeedra</t>
-  </si>
-  <si>
     <t>https://replay.pokemonshowdown.com/gen9nationaldexmonotype-2700276310</t>
   </si>
   <si>
@@ -456,9 +447,6 @@
   </si>
   <si>
     <t>Willy</t>
-  </si>
-  <si>
-    <t>Mouka</t>
   </si>
   <si>
     <t>https://replay.pokemonshowdown.com/gen9randombattle-2696332664</t>
@@ -1133,13 +1121,13 @@
         <v>31</v>
       </c>
       <c r="H2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I2" t="s">
         <v>32</v>
       </c>
       <c r="J2" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L2" t="s">
         <v>33</v>
@@ -1174,10 +1162,10 @@
         <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
         <v>28</v>
@@ -1192,13 +1180,13 @@
         <v>31</v>
       </c>
       <c r="H3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I3" t="s">
         <v>32</v>
       </c>
       <c r="J3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L3" t="s">
         <v>33</v>
@@ -1251,13 +1239,13 @@
         <v>31</v>
       </c>
       <c r="H4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I4" t="s">
         <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="L4" t="s">
         <v>33</v>
@@ -1310,13 +1298,13 @@
         <v>31</v>
       </c>
       <c r="H5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I5" t="s">
         <v>32</v>
       </c>
       <c r="J5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L5" t="s">
         <v>43</v>
@@ -1369,13 +1357,13 @@
         <v>31</v>
       </c>
       <c r="H6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I6" t="s">
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L6" t="s">
         <v>43</v>
@@ -1428,13 +1416,13 @@
         <v>31</v>
       </c>
       <c r="H7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I7" t="s">
         <v>32</v>
       </c>
       <c r="J7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L7" t="s">
         <v>43</v>
@@ -1466,7 +1454,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1487,13 +1475,13 @@
         <v>31</v>
       </c>
       <c r="H8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I8" t="s">
         <v>32</v>
       </c>
       <c r="J8" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L8" t="s">
         <v>33</v>
@@ -1525,13 +1513,13 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
         <v>28</v>
@@ -1585,13 +1573,13 @@
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
         <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
@@ -1606,13 +1594,13 @@
         <v>31</v>
       </c>
       <c r="H10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I10" t="s">
         <v>32</v>
       </c>
       <c r="J10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L10" t="s">
         <v>33</v>
@@ -1665,13 +1653,13 @@
         <v>31</v>
       </c>
       <c r="H11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I11" t="s">
         <v>32</v>
       </c>
       <c r="J11" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L11" t="s">
         <v>43</v>
@@ -1724,13 +1712,13 @@
         <v>31</v>
       </c>
       <c r="H12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I12" t="s">
         <v>32</v>
       </c>
       <c r="J12" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L12" t="s">
         <v>43</v>
@@ -1783,13 +1771,13 @@
         <v>31</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I13" t="s">
         <v>32</v>
       </c>
       <c r="J13" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L13" t="s">
         <v>43</v>
@@ -1821,13 +1809,13 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s">
         <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
         <v>28</v>
@@ -1842,13 +1830,13 @@
         <v>31</v>
       </c>
       <c r="H14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I14" t="s">
         <v>32</v>
       </c>
       <c r="J14" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="L14" t="s">
         <v>50</v>
@@ -1880,13 +1868,13 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C15" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s">
         <v>28</v>
@@ -1901,13 +1889,13 @@
         <v>31</v>
       </c>
       <c r="H15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I15" t="s">
         <v>32</v>
       </c>
       <c r="J15" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L15" t="s">
         <v>43</v>
@@ -1939,13 +1927,13 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B16" t="s">
         <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
         <v>28</v>
@@ -1960,13 +1948,13 @@
         <v>31</v>
       </c>
       <c r="H16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="I16" t="s">
         <v>32</v>
       </c>
       <c r="J16" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="L16" t="s">
         <v>43</v>
@@ -2001,7 +1989,7 @@
         <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C17" t="s">
         <v>58</v>
@@ -2019,13 +2007,13 @@
         <v>31</v>
       </c>
       <c r="H17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I17" t="s">
         <v>32</v>
       </c>
       <c r="J17" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s">
         <v>43</v>
@@ -2060,10 +2048,10 @@
         <v>58</v>
       </c>
       <c r="B18" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C18" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
         <v>28</v>
@@ -2078,13 +2066,13 @@
         <v>31</v>
       </c>
       <c r="H18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I18" t="s">
         <v>32</v>
       </c>
       <c r="J18" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L18" t="s">
         <v>43</v>
@@ -2116,13 +2104,13 @@
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B19" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D19" t="s">
         <v>28</v>
@@ -2137,13 +2125,13 @@
         <v>31</v>
       </c>
       <c r="H19" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="I19" t="s">
         <v>32</v>
       </c>
       <c r="J19" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="L19" t="s">
         <v>33</v>
@@ -2175,7 +2163,7 @@
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B20" t="s">
         <v>58</v>
@@ -2196,13 +2184,13 @@
         <v>31</v>
       </c>
       <c r="H20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="I20" t="s">
         <v>32</v>
       </c>
       <c r="J20" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="L20" t="s">
         <v>50</v>
@@ -2234,7 +2222,7 @@
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B21" t="s">
         <v>62</v>
@@ -2255,13 +2243,13 @@
         <v>31</v>
       </c>
       <c r="H21" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="I21" t="s">
         <v>32</v>
       </c>
       <c r="J21" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="L21" t="s">
         <v>33</v>
@@ -2296,10 +2284,10 @@
         <v>62</v>
       </c>
       <c r="B22" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C22" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
@@ -2314,13 +2302,13 @@
         <v>31</v>
       </c>
       <c r="H22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I22" t="s">
         <v>32</v>
       </c>
       <c r="J22" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L22" t="s">
         <v>43</v>
@@ -2355,10 +2343,10 @@
         <v>62</v>
       </c>
       <c r="B23" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C23" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
@@ -2373,13 +2361,13 @@
         <v>31</v>
       </c>
       <c r="H23" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I23" t="s">
         <v>32</v>
       </c>
       <c r="J23" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L23" t="s">
         <v>43</v>
@@ -2411,13 +2399,13 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B24" t="s">
         <v>72</v>
       </c>
       <c r="C24" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D24" t="s">
         <v>28</v>
@@ -2432,13 +2420,13 @@
         <v>31</v>
       </c>
       <c r="H24" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I24" t="s">
         <v>32</v>
       </c>
       <c r="J24" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L24" t="s">
         <v>43</v>
@@ -2473,7 +2461,7 @@
         <v>72</v>
       </c>
       <c r="B25" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C25" t="s">
         <v>72</v>
@@ -2491,13 +2479,13 @@
         <v>31</v>
       </c>
       <c r="H25" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I25" t="s">
         <v>32</v>
       </c>
       <c r="J25" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s">
         <v>43</v>
@@ -2550,13 +2538,13 @@
         <v>31</v>
       </c>
       <c r="H26" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I26" t="s">
         <v>32</v>
       </c>
       <c r="J26" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L26" t="s">
         <v>43</v>
@@ -2591,10 +2579,10 @@
         <v>72</v>
       </c>
       <c r="B27" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C27" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D27" t="s">
         <v>28</v>
@@ -2609,13 +2597,13 @@
         <v>31</v>
       </c>
       <c r="H27" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I27" t="s">
         <v>32</v>
       </c>
       <c r="J27" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L27" t="s">
         <v>43</v>
@@ -2668,13 +2656,13 @@
         <v>31</v>
       </c>
       <c r="H28" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I28" t="s">
         <v>32</v>
       </c>
       <c r="J28" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L28" t="s">
         <v>43</v>
@@ -2709,10 +2697,10 @@
         <v>77</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C29" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D29" t="s">
         <v>28</v>
@@ -2727,13 +2715,13 @@
         <v>31</v>
       </c>
       <c r="H29" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I29" t="s">
         <v>32</v>
       </c>
       <c r="J29" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L29" t="s">
         <v>43</v>
@@ -2765,13 +2753,13 @@
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B30" t="s">
         <v>72</v>
       </c>
       <c r="C30" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D30" t="s">
         <v>28</v>
@@ -2786,13 +2774,13 @@
         <v>31</v>
       </c>
       <c r="H30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I30" t="s">
         <v>32</v>
       </c>
       <c r="J30" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L30" t="s">
         <v>43</v>
@@ -2824,13 +2812,13 @@
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s">
         <v>77</v>
       </c>
       <c r="C31" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="D31" t="s">
         <v>28</v>
@@ -2845,13 +2833,13 @@
         <v>31</v>
       </c>
       <c r="H31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I31" t="s">
         <v>32</v>
       </c>
       <c r="J31" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L31" t="s">
         <v>43</v>
@@ -2883,13 +2871,13 @@
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="B32" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C32" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D32" t="s">
         <v>28</v>
@@ -2904,13 +2892,13 @@
         <v>31</v>
       </c>
       <c r="H32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I32" t="s">
         <v>32</v>
       </c>
       <c r="J32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L32" t="s">
         <v>50</v>
@@ -2928,7 +2916,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="T32">
         <v>8</v>
@@ -2937,18 +2925,18 @@
         <v>28</v>
       </c>
       <c r="AA32" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>165</v>
+      </c>
+      <c r="B33" t="s">
         <v>169</v>
       </c>
-      <c r="B33" t="s">
-        <v>173</v>
-      </c>
       <c r="C33" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D33" t="s">
         <v>28</v>
@@ -2963,13 +2951,13 @@
         <v>31</v>
       </c>
       <c r="H33" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I33" t="s">
         <v>32</v>
       </c>
       <c r="J33" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L33" t="s">
         <v>43</v>
@@ -2987,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -2996,18 +2984,18 @@
         <v>28</v>
       </c>
       <c r="AA33" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C34" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D34" t="s">
         <v>28</v>
@@ -3022,13 +3010,13 @@
         <v>31</v>
       </c>
       <c r="H34" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I34" t="s">
         <v>32</v>
       </c>
       <c r="J34" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L34" t="s">
         <v>43</v>
@@ -3046,7 +3034,7 @@
         <v>0</v>
       </c>
       <c r="S34" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3055,15 +3043,15 @@
         <v>28</v>
       </c>
       <c r="AA34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C35" t="s">
         <v>27</v>
@@ -3081,13 +3069,13 @@
         <v>31</v>
       </c>
       <c r="H35" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I35" t="s">
         <v>32</v>
       </c>
       <c r="J35" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L35" t="s">
         <v>43</v>
@@ -3114,18 +3102,18 @@
         <v>28</v>
       </c>
       <c r="AA35" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C36" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D36" t="s">
         <v>28</v>
@@ -3140,13 +3128,13 @@
         <v>31</v>
       </c>
       <c r="H36" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I36" t="s">
         <v>32</v>
       </c>
       <c r="J36" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L36" t="s">
         <v>50</v>
@@ -3164,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="S36" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="T36">
         <v>8</v>
@@ -3173,18 +3161,18 @@
         <v>28</v>
       </c>
       <c r="AA36" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
         <v>28</v>
@@ -3199,13 +3187,13 @@
         <v>31</v>
       </c>
       <c r="H37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I37" t="s">
         <v>32</v>
       </c>
       <c r="J37" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L37" t="s">
         <v>43</v>
@@ -3223,7 +3211,7 @@
         <v>0</v>
       </c>
       <c r="S37" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3232,18 +3220,18 @@
         <v>28</v>
       </c>
       <c r="AA37" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D38" t="s">
         <v>28</v>
@@ -3258,13 +3246,13 @@
         <v>31</v>
       </c>
       <c r="H38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="I38" t="s">
         <v>32</v>
       </c>
       <c r="J38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="L38" t="s">
         <v>50</v>
@@ -3282,7 +3270,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="T38">
         <v>9</v>
@@ -3291,18 +3279,18 @@
         <v>28</v>
       </c>
       <c r="AA38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="39" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B39" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C39" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D39" t="s">
         <v>28</v>
@@ -3317,13 +3305,13 @@
         <v>31</v>
       </c>
       <c r="H39" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I39" t="s">
         <v>32</v>
       </c>
       <c r="J39" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L39" t="s">
         <v>43</v>
@@ -3341,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="T39">
         <v>9</v>
@@ -3350,18 +3338,18 @@
         <v>28</v>
       </c>
       <c r="AA39" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="40" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C40" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D40" t="s">
         <v>28</v>
@@ -3376,13 +3364,13 @@
         <v>31</v>
       </c>
       <c r="H40" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I40" t="s">
         <v>32</v>
       </c>
       <c r="J40" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L40" t="s">
         <v>43</v>
@@ -3400,7 +3388,7 @@
         <v>0</v>
       </c>
       <c r="S40" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="T40">
         <v>9</v>
@@ -3409,18 +3397,18 @@
         <v>28</v>
       </c>
       <c r="AA40" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="41" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D41" t="s">
         <v>28</v>
@@ -3435,13 +3423,13 @@
         <v>31</v>
       </c>
       <c r="H41" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I41" t="s">
         <v>32</v>
       </c>
       <c r="J41" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L41" t="s">
         <v>43</v>
@@ -3459,7 +3447,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="T41">
         <v>9</v>
@@ -3468,18 +3456,18 @@
         <v>28</v>
       </c>
       <c r="AA41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B42" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C42" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D42" t="s">
         <v>28</v>
@@ -3494,13 +3482,13 @@
         <v>31</v>
       </c>
       <c r="H42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="I42" t="s">
         <v>32</v>
       </c>
       <c r="J42" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L42" t="s">
         <v>43</v>
@@ -3518,7 +3506,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="T42">
         <v>9</v>
@@ -3527,24 +3515,24 @@
         <v>28</v>
       </c>
       <c r="AA42" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C43" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D43" t="s">
         <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F43" t="s">
         <v>30</v>
@@ -3553,13 +3541,13 @@
         <v>31</v>
       </c>
       <c r="H43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I43" t="s">
         <v>32</v>
       </c>
       <c r="J43" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L43" t="s">
         <v>43</v>
@@ -3577,7 +3565,7 @@
         <v>0</v>
       </c>
       <c r="S43" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T43">
         <v>9</v>
@@ -3586,18 +3574,18 @@
         <v>28</v>
       </c>
       <c r="AA43" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D44" t="s">
         <v>28</v>
@@ -3612,13 +3600,13 @@
         <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I44" t="s">
         <v>32</v>
       </c>
       <c r="J44" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L44" t="s">
         <v>43</v>
@@ -3636,7 +3624,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="T44">
         <v>9</v>
@@ -3645,24 +3633,24 @@
         <v>28</v>
       </c>
       <c r="AA44" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B45" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C45" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D45" t="s">
         <v>28</v>
       </c>
       <c r="E45" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F45" t="s">
         <v>30</v>
@@ -3671,13 +3659,13 @@
         <v>31</v>
       </c>
       <c r="H45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I45" t="s">
         <v>32</v>
       </c>
       <c r="J45" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s">
         <v>43</v>
@@ -3695,7 +3683,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="T45">
         <v>9</v>
@@ -3704,18 +3692,18 @@
         <v>28</v>
       </c>
       <c r="AA45" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D46" t="s">
         <v>28</v>
@@ -3730,13 +3718,13 @@
         <v>31</v>
       </c>
       <c r="H46" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I46" t="s">
         <v>32</v>
       </c>
       <c r="J46" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s">
         <v>43</v>
@@ -3754,7 +3742,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -3763,18 +3751,18 @@
         <v>28</v>
       </c>
       <c r="AA46" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>97</v>
+      </c>
+      <c r="B47" t="s">
         <v>100</v>
       </c>
-      <c r="B47" t="s">
-        <v>103</v>
-      </c>
       <c r="C47" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D47" t="s">
         <v>28</v>
@@ -3789,13 +3777,13 @@
         <v>31</v>
       </c>
       <c r="H47" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I47" t="s">
         <v>32</v>
       </c>
       <c r="J47" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L47" t="s">
         <v>43</v>
@@ -3813,7 +3801,7 @@
         <v>0</v>
       </c>
       <c r="S47" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="T47">
         <v>9</v>
@@ -3822,18 +3810,18 @@
         <v>28</v>
       </c>
       <c r="AA47" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B48" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D48" t="s">
         <v>28</v>
@@ -3848,13 +3836,13 @@
         <v>31</v>
       </c>
       <c r="H48" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="I48" t="s">
         <v>32</v>
       </c>
       <c r="J48" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="L48" t="s">
         <v>33</v>
@@ -3872,7 +3860,7 @@
         <v>0</v>
       </c>
       <c r="S48" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="T48">
         <v>9</v>
@@ -3881,18 +3869,18 @@
         <v>28</v>
       </c>
       <c r="AA48" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B49" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C49" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D49" t="s">
         <v>28</v>
@@ -3907,13 +3895,13 @@
         <v>31</v>
       </c>
       <c r="H49" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I49" t="s">
         <v>32</v>
       </c>
       <c r="J49" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L49" t="s">
         <v>43</v>
@@ -3931,7 +3919,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="T49">
         <v>9</v>
@@ -3940,24 +3928,24 @@
         <v>28</v>
       </c>
       <c r="AA49" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B50" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C50" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D50" t="s">
         <v>28</v>
       </c>
       <c r="E50" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F50" t="s">
         <v>30</v>
@@ -3966,13 +3954,13 @@
         <v>31</v>
       </c>
       <c r="H50" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I50" t="s">
         <v>32</v>
       </c>
       <c r="J50" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L50" t="s">
         <v>43</v>
@@ -3990,7 +3978,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="T50">
         <v>9</v>
@@ -3999,18 +3987,18 @@
         <v>28</v>
       </c>
       <c r="AA50" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C51" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D51" t="s">
         <v>28</v>
@@ -4025,13 +4013,13 @@
         <v>31</v>
       </c>
       <c r="H51" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="I51" t="s">
         <v>32</v>
       </c>
       <c r="J51" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s">
         <v>43</v>
@@ -4049,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="S51" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="T51">
         <v>9</v>
@@ -4058,18 +4046,18 @@
         <v>28</v>
       </c>
       <c r="AA51" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B52" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C52" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D52" t="s">
         <v>28</v>
@@ -4084,13 +4072,13 @@
         <v>31</v>
       </c>
       <c r="H52" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="I52" t="s">
         <v>32</v>
       </c>
       <c r="J52" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L52" t="s">
         <v>43</v>
@@ -4108,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="S52" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="T52">
         <v>9</v>
@@ -4117,24 +4105,24 @@
         <v>28</v>
       </c>
       <c r="AA52" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="B53" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C53" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D53" t="s">
         <v>28</v>
       </c>
       <c r="E53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F53" t="s">
         <v>30</v>
@@ -4143,13 +4131,13 @@
         <v>31</v>
       </c>
       <c r="H53" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I53" t="s">
         <v>32</v>
       </c>
       <c r="J53" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L53" t="s">
         <v>43</v>
@@ -4167,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="S53" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="T53">
         <v>9</v>
@@ -4176,24 +4164,24 @@
         <v>28</v>
       </c>
       <c r="AA53" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B54" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C54" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D54" t="s">
         <v>28</v>
       </c>
       <c r="E54" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F54" t="s">
         <v>30</v>
@@ -4226,7 +4214,7 @@
         <v>0</v>
       </c>
       <c r="S54" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="T54">
         <v>9</v>
@@ -4235,18 +4223,18 @@
         <v>28</v>
       </c>
       <c r="AA54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C55" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="D55" t="s">
         <v>28</v>
@@ -4285,7 +4273,7 @@
         <v>0</v>
       </c>
       <c r="S55" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="T55">
         <v>9</v>
@@ -4294,18 +4282,18 @@
         <v>28</v>
       </c>
       <c r="AA55" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B56" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C56" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D56" t="s">
         <v>28</v>
@@ -4344,7 +4332,7 @@
         <v>0</v>
       </c>
       <c r="S56" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="T56">
         <v>9</v>
@@ -4353,18 +4341,18 @@
         <v>28</v>
       </c>
       <c r="AA56" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B57" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C57" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D57" t="s">
         <v>28</v>
@@ -4379,13 +4367,13 @@
         <v>31</v>
       </c>
       <c r="H57" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="I57" t="s">
         <v>32</v>
       </c>
       <c r="J57" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="L57" t="s">
         <v>43</v>
@@ -4403,7 +4391,7 @@
         <v>0</v>
       </c>
       <c r="S57" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="T57">
         <v>9</v>
@@ -4412,18 +4400,18 @@
         <v>28</v>
       </c>
       <c r="AA57" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B58" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="C58" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D58" t="s">
         <v>28</v>
@@ -4438,13 +4426,13 @@
         <v>31</v>
       </c>
       <c r="H58" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I58" t="s">
         <v>32</v>
       </c>
       <c r="J58" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L58" t="s">
         <v>43</v>
@@ -4462,7 +4450,7 @@
         <v>0</v>
       </c>
       <c r="S58" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="T58">
         <v>9</v>
@@ -4471,18 +4459,18 @@
         <v>28</v>
       </c>
       <c r="AA58" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B59" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C59" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D59" t="s">
         <v>28</v>
@@ -4521,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="S59" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="T59">
         <v>9</v>
@@ -4530,18 +4518,18 @@
         <v>28</v>
       </c>
       <c r="AA59" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B60" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C60" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D60" t="s">
         <v>28</v>
@@ -4556,13 +4544,13 @@
         <v>31</v>
       </c>
       <c r="H60" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I60" t="s">
         <v>32</v>
       </c>
       <c r="J60" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L60" t="s">
         <v>43</v>
@@ -4580,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="T60">
         <v>2</v>
@@ -4589,18 +4577,18 @@
         <v>28</v>
       </c>
       <c r="AA60" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B61" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C61" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D61" t="s">
         <v>28</v>
@@ -4615,13 +4603,13 @@
         <v>31</v>
       </c>
       <c r="H61" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="I61" t="s">
         <v>32</v>
       </c>
       <c r="J61" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="L61" t="s">
         <v>43</v>
@@ -4639,7 +4627,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="T61">
         <v>9</v>
@@ -4648,18 +4636,18 @@
         <v>28</v>
       </c>
       <c r="AA61" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B62" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="D62" t="s">
         <v>28</v>
@@ -4674,13 +4662,13 @@
         <v>31</v>
       </c>
       <c r="H62" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I62" t="s">
         <v>32</v>
       </c>
       <c r="J62" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L62" t="s">
         <v>43</v>
@@ -4698,7 +4686,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="T62">
         <v>9</v>
@@ -4707,39 +4695,39 @@
         <v>28</v>
       </c>
       <c r="AA62" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
+        <v>179</v>
+      </c>
+      <c r="C63" t="s">
+        <v>179</v>
+      </c>
+      <c r="D63" t="s">
+        <v>28</v>
+      </c>
+      <c r="E63" t="s">
+        <v>113</v>
+      </c>
+      <c r="F63" t="s">
+        <v>30</v>
+      </c>
+      <c r="G63" t="s">
+        <v>31</v>
+      </c>
+      <c r="H63" t="s">
         <v>183</v>
       </c>
-      <c r="C63" t="s">
+      <c r="I63" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63" t="s">
         <v>183</v>
-      </c>
-      <c r="D63" t="s">
-        <v>28</v>
-      </c>
-      <c r="E63" t="s">
-        <v>116</v>
-      </c>
-      <c r="F63" t="s">
-        <v>30</v>
-      </c>
-      <c r="G63" t="s">
-        <v>31</v>
-      </c>
-      <c r="H63" t="s">
-        <v>187</v>
-      </c>
-      <c r="I63" t="s">
-        <v>32</v>
-      </c>
-      <c r="J63" t="s">
-        <v>187</v>
       </c>
       <c r="L63" t="s">
         <v>43</v>
@@ -4757,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="T63">
         <v>9</v>
@@ -4766,18 +4754,18 @@
         <v>28</v>
       </c>
       <c r="AA63" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B64" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C64" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="D64" t="s">
         <v>28</v>
@@ -4792,13 +4780,13 @@
         <v>31</v>
       </c>
       <c r="H64" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I64" t="s">
         <v>32</v>
       </c>
       <c r="J64" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L64" t="s">
         <v>43</v>
@@ -4816,7 +4804,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="T64">
         <v>9</v>
@@ -4825,24 +4813,24 @@
         <v>28</v>
       </c>
       <c r="AA64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
         <v>28</v>
       </c>
       <c r="E65" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F65" t="s">
         <v>30</v>
@@ -4851,13 +4839,13 @@
         <v>31</v>
       </c>
       <c r="H65" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I65" t="s">
         <v>32</v>
       </c>
       <c r="J65" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L65" t="s">
         <v>43</v>
@@ -4875,7 +4863,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="T65">
         <v>9</v>
@@ -4884,39 +4872,39 @@
         <v>28</v>
       </c>
       <c r="AA65" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>179</v>
+      </c>
+      <c r="B66" t="s">
+        <v>126</v>
+      </c>
+      <c r="C66" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" t="s">
+        <v>28</v>
+      </c>
+      <c r="E66" t="s">
+        <v>132</v>
+      </c>
+      <c r="F66" t="s">
+        <v>30</v>
+      </c>
+      <c r="G66" t="s">
+        <v>31</v>
+      </c>
+      <c r="H66" t="s">
         <v>183</v>
       </c>
-      <c r="B66" t="s">
-        <v>129</v>
-      </c>
-      <c r="C66" t="s">
+      <c r="I66" t="s">
+        <v>32</v>
+      </c>
+      <c r="J66" t="s">
         <v>183</v>
-      </c>
-      <c r="D66" t="s">
-        <v>28</v>
-      </c>
-      <c r="E66" t="s">
-        <v>135</v>
-      </c>
-      <c r="F66" t="s">
-        <v>30</v>
-      </c>
-      <c r="G66" t="s">
-        <v>31</v>
-      </c>
-      <c r="H66" t="s">
-        <v>187</v>
-      </c>
-      <c r="I66" t="s">
-        <v>32</v>
-      </c>
-      <c r="J66" t="s">
-        <v>187</v>
       </c>
       <c r="L66" t="s">
         <v>43</v>
@@ -4934,7 +4922,7 @@
         <v>0</v>
       </c>
       <c r="S66" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="T66">
         <v>9</v>
@@ -4943,18 +4931,18 @@
         <v>28</v>
       </c>
       <c r="AA66" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B67" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D67" t="s">
         <v>28</v>
@@ -4969,13 +4957,13 @@
         <v>31</v>
       </c>
       <c r="H67" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I67" t="s">
         <v>32</v>
       </c>
       <c r="J67" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s">
         <v>43</v>
@@ -4993,7 +4981,7 @@
         <v>0</v>
       </c>
       <c r="S67" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="T67">
         <v>9</v>
@@ -5002,24 +4990,24 @@
         <v>28</v>
       </c>
       <c r="AA67" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D68" t="s">
         <v>28</v>
       </c>
       <c r="E68" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F68" t="s">
         <v>30</v>
@@ -5028,13 +5016,13 @@
         <v>31</v>
       </c>
       <c r="H68" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I68" t="s">
         <v>32</v>
       </c>
       <c r="J68" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L68" t="s">
         <v>43</v>
@@ -5052,7 +5040,7 @@
         <v>0</v>
       </c>
       <c r="S68" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="T68">
         <v>9</v>
@@ -5061,18 +5049,18 @@
         <v>28</v>
       </c>
       <c r="AA68" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B69" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C69" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="D69" t="s">
         <v>28</v>
@@ -5087,13 +5075,13 @@
         <v>31</v>
       </c>
       <c r="H69" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I69" t="s">
         <v>32</v>
       </c>
       <c r="J69" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L69" t="s">
         <v>43</v>
@@ -5111,7 +5099,7 @@
         <v>0</v>
       </c>
       <c r="S69" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="T69">
         <v>9</v>
@@ -5120,18 +5108,18 @@
         <v>28</v>
       </c>
       <c r="AA69" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
         <v>139</v>
       </c>
-      <c r="B70" t="s">
-        <v>143</v>
-      </c>
       <c r="C70" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D70" t="s">
         <v>28</v>
@@ -5146,13 +5134,13 @@
         <v>31</v>
       </c>
       <c r="H70" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I70" t="s">
         <v>32</v>
       </c>
       <c r="J70" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L70" t="s">
         <v>43</v>
@@ -5170,7 +5158,7 @@
         <v>0</v>
       </c>
       <c r="S70" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="T70">
         <v>9</v>
@@ -5179,18 +5167,18 @@
         <v>28</v>
       </c>
       <c r="AA70" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B71" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C71" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D71" t="s">
         <v>28</v>
@@ -5205,13 +5193,13 @@
         <v>31</v>
       </c>
       <c r="H71" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I71" t="s">
         <v>32</v>
       </c>
       <c r="J71" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L71" t="s">
         <v>33</v>
@@ -5229,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="S71" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="T71">
         <v>9</v>
@@ -5238,18 +5226,18 @@
         <v>28</v>
       </c>
       <c r="AA71" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B72" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C72" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="D72" t="s">
         <v>28</v>
@@ -5264,13 +5252,13 @@
         <v>31</v>
       </c>
       <c r="H72" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="I72" t="s">
         <v>32</v>
       </c>
       <c r="J72" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="L72" t="s">
         <v>43</v>
@@ -5288,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="S72" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="T72">
         <v>9</v>
@@ -5297,24 +5285,24 @@
         <v>28</v>
       </c>
       <c r="AA72" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B73" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D73" t="s">
         <v>28</v>
       </c>
       <c r="E73" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F73" t="s">
         <v>30</v>
@@ -5323,13 +5311,13 @@
         <v>31</v>
       </c>
       <c r="H73" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="I73" t="s">
         <v>32</v>
       </c>
       <c r="J73" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="L73" t="s">
         <v>43</v>
@@ -5347,7 +5335,7 @@
         <v>0</v>
       </c>
       <c r="S73" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="T73">
         <v>9</v>
@@ -5356,18 +5344,18 @@
         <v>28</v>
       </c>
       <c r="AA73" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C74" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="D74" t="s">
         <v>28</v>
@@ -5382,13 +5370,13 @@
         <v>31</v>
       </c>
       <c r="H74" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I74" t="s">
         <v>32</v>
       </c>
       <c r="J74" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L74" t="s">
         <v>43</v>
@@ -5406,7 +5394,7 @@
         <v>0</v>
       </c>
       <c r="S74" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="T74">
         <v>9</v>
@@ -5415,18 +5403,18 @@
         <v>28</v>
       </c>
       <c r="AA74" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B75" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" t="s">
         <v>139</v>
-      </c>
-      <c r="C75" t="s">
-        <v>143</v>
       </c>
       <c r="D75" t="s">
         <v>28</v>
@@ -5441,13 +5429,13 @@
         <v>31</v>
       </c>
       <c r="H75" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="I75" t="s">
         <v>32</v>
       </c>
       <c r="J75" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L75" t="s">
         <v>43</v>
@@ -5465,7 +5453,7 @@
         <v>0</v>
       </c>
       <c r="S75" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="T75">
         <v>9</v>
@@ -5474,18 +5462,18 @@
         <v>28</v>
       </c>
       <c r="AA75" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B76" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C76" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D76" t="s">
         <v>28</v>
@@ -5500,13 +5488,13 @@
         <v>31</v>
       </c>
       <c r="H76" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="I76" t="s">
         <v>32</v>
       </c>
       <c r="J76" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="L76" t="s">
         <v>43</v>
@@ -5524,7 +5512,7 @@
         <v>0</v>
       </c>
       <c r="S76" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="T76">
         <v>8</v>
@@ -5533,18 +5521,18 @@
         <v>28</v>
       </c>
       <c r="AA76" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B77" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C77" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D77" t="s">
         <v>28</v>
@@ -5559,13 +5547,13 @@
         <v>31</v>
       </c>
       <c r="H77" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="I77" t="s">
         <v>32</v>
       </c>
       <c r="J77" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="L77" t="s">
         <v>43</v>
@@ -5583,7 +5571,7 @@
         <v>0</v>
       </c>
       <c r="S77" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="T77">
         <v>9</v>
@@ -5592,18 +5580,18 @@
         <v>28</v>
       </c>
       <c r="AA77" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B78" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C78" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D78" t="s">
         <v>28</v>
@@ -5618,13 +5606,13 @@
         <v>31</v>
       </c>
       <c r="H78" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="I78" t="s">
         <v>32</v>
       </c>
       <c r="J78" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="L78" t="s">
         <v>33</v>
@@ -5642,7 +5630,7 @@
         <v>0</v>
       </c>
       <c r="S78" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="T78">
         <v>9</v>
@@ -5651,7 +5639,7 @@
         <v>28</v>
       </c>
       <c r="AA78" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -5671,10 +5659,10 @@
         <v>25</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -5704,7 +5692,7 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -5726,7 +5714,7 @@
         <v>60</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="C6">
         <v>2</v>
@@ -5748,7 +5736,7 @@
         <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -5770,7 +5758,7 @@
         <v>75</v>
       </c>
       <c r="B10" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -5800,7 +5788,7 @@
         <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -5808,10 +5796,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -5819,10 +5807,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C15">
         <v>4</v>
@@ -5830,10 +5818,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C16">
         <v>5</v>
@@ -5841,18 +5829,18 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="C18">
         <v>4</v>
@@ -5860,10 +5848,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -5871,10 +5859,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C20">
         <v>2</v>
@@ -5882,26 +5870,26 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B22" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C23">
         <v>4</v>
@@ -5909,10 +5897,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B24" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -5920,10 +5908,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B25" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -5931,10 +5919,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B26" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -5942,10 +5930,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -5953,10 +5941,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -5964,18 +5952,18 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>123</v>
+      </c>
+      <c r="B29" t="s">
         <v>126</v>
-      </c>
-      <c r="B29" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -5983,10 +5971,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C31">
         <v>4</v>
@@ -5994,10 +5982,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C32">
         <v>1</v>
@@ -6005,10 +5993,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C33">
         <v>2</v>
@@ -6023,6 +6011,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="4" max="4" width="35.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
@@ -6035,10 +6029,10 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>32</v>
@@ -6055,73 +6049,73 @@
         <v>40</v>
       </c>
       <c r="D2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="D3" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E3" t="s">
-        <v>91</v>
+        <v>27</v>
       </c>
       <c r="F3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>162</v>
       </c>
       <c r="F4" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F5" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
